--- a/quotations.xlsx
+++ b/quotations.xlsx
@@ -893,13 +893,13 @@
     <t>For example: now, with the new Java versions, you write much less code; you abandon those more primitive algorithms, like doing algorithms to go through collections to find a certain element and make a return from it.</t>
   </si>
   <si>
+    <t>Python has gone through an evolutionary process, which is why, for many years, you had two versions of Python, the 2.7 x and the version 3. We even used to joke that Python has lost a few users because of that; thanks to Data Science, it has become the language it is nowadays: Machine Learning, Data Science, etc. But it has always been an excellent general-purpose language, including for web purposes, so the language evolution for software evolution is crucial. I was able to keep up with this type of evolution in several languages. Scala pushed Java to improvement, C# also pushed Java to improvement because Java fell behind, they saw how losing that thread of evolution could have an impact on the business</t>
+  </si>
+  <si>
     <t>Python has gone through an evolutionary process, which is why, for many years, you had two versions of Python, the 2.7 x and the version 3. We even used to joke that Python has lost a few users because of that; thanks to Data Science, it has become the language it is nowadays: Machine Learning, Data Science, etc. But it has always been an excellent general-purpose language, including for web purposes, so the language evolution for software evolution is crucial. I was able to keep up with this type of evolution in several languages. Scala pushed Java to improvement, C# also pushed Java to improvement because Java fell behind, they saw how losing that thread of evolution could have an impact on the business.</t>
   </si>
   <si>
     <t>Programming language migration</t>
-  </si>
-  <si>
-    <t>Python has gone through an evolutionary process, which is why, for many years, you had two versions of Python, the 2.7 x and the version 3. We even used to joke that Python has lost a few users because of that; thanks to Data Science, it has become the language it is nowadays: Machine Learning, Data Science, etc. But it has always been an excellent general-purpose language, including for web purposes, so the language evolution for software evolution is crucial. I was able to keep up with this type of evolution in several languages. Scala pushed Java to improvement, C# also pushed Java to improvement because Java fell behind, they saw how losing that thread of evolution could have an impact on the business</t>
   </si>
   <si>
     <t>One of the most important aspects of evolving code, as the language evolves, is the need for migrating. One notorious language for giving developers headaches because of its ways of evolving is Scala. Its philosophy is: whatever becomes deprecated today, tomorrow will be lost. Code becomes unusable from one version to another, and the cost associated with leaving your code behind by two or three versions of the language is very high, both in time and energy spent in updating it. As a developer, it is very important to your day-to-day work to follow along with the language evolution, because it diminishes the cost of migrating an old codebase, which is hard to deal with, and saves you time down the road. Furthermore, it improves performance, since languages evolve in many aspects. Think about Ruby. From version 2.0 to version 3.0, it took an important step in improving performance. I went to a lecture by Koichi Sasada, who rewrote the entire garbage collector. He managed to make the garbage collector work three times faster, even though he said the goal was to make it ten times faster. Anyway, increasing its performance was an important improvement regarding its competitors, other faster and interpreted and compiled languages, like Python, Java, and C#. It is critically important that you are evolving your codebase as languages evolve so that you get new features, performance gains, security bug fixes, and avoid the trauma of migration.</t>
@@ -1136,13 +1136,13 @@
     <t>Some of these languages that have wasted a lot of time on retrocompatibility, like JavaScript or PHP, are languages that pile up workarounds on language semantics with time. These changes that aim to make language simpler to understand, to remember, consequently make it harder to confuse and make a mistake, are also changes that make me want to evolve.</t>
   </si>
   <si>
+    <t>I think the main challenge is the code base size. If your code base is big, you may need to test a lot of code. I’ll number it: code base size, application stability. If you have a quite stable application, even if it uses a previous version of the language, it’s tough to pay the price of having to revalidate everything that was in that application. Being able to perform a gradual migration is a good thing: in one part you evolve language, the other remain compatible with the previous version. This is what mitigates the issue with a big code base, too large for testing. I’ll return to the last question, that was about the reasons for changing: A reason for changing is discontinuing, sometimes there’s no other way, even if the application is stable. For example, with Python, the language stopped receiving maintenance, it ends up not being purely an issue of being able to add new features, but also an issue of not receiving any patch if they find a security flaw in this interpreter version, and you end up having no choice but to update. Back to the challenges, if the application is quite stable, it's hard convincing yourself that it’s worthwhile to update just to get a new feature, when this could mean losing application stability. If it’s a new feature that helps you perform maintenance and an application that has just been started or is riddled with bugs, it’s worth it. Theoretically, through doing this, the bug rate will get lower with time. Having a large application makes it harder, though it could be done gradually. When frameworks have drastic updates, they provide a migrating tool, there are also migrating guides, but preferably, an automated migration tool helps a lot. It’s a challenge if there are retrocompatibility issues, especially if they’re not algorithmically soluble. For example, from Python 2 to Python 3, they provided a migration tool, and there were changes like: In Python 2, print was a keyword, and in Python 3, a function, you could replace all print, space, anything for a print, open parenthesis, that same thing. It was algorithmical to do it. You could make a tool, even if the language update doesn't provide it, you could write it yourself and be quite confident with the results. If not, you’ll depend a lot on automated tests and this is another challenge. If your application has low test coverage, the previous challenges are amplified, and if you have a good test coverage, you can rest assured that it will be possible to identify where an issue is, as long as you run a series of tests on the migration.</t>
+  </si>
+  <si>
     <t>I think the main challenge is the code base size. If your code base is big, you may need to test a lot of code. I’ll number it: code base size, application stability. If you have a quite stable application, even if it uses a previous version of the language, it’s tough to pay the price of having to revalidate everything that was in that application.</t>
   </si>
   <si>
     <t>Project complexity might hinder SCR efforts, Relevance of regression/automated testing, SCR requires careful planning, Analyse costs/benefits before rejuvenate</t>
-  </si>
-  <si>
-    <t>I think the main challenge is the code base size. If your code base is big, you may need to test a lot of code. I’ll number it: code base size, application stability. If you have a quite stable application, even if it uses a previous version of the language, it’s tough to pay the price of having to revalidate everything that was in that application. Being able to perform a gradual migration is a good thing: in one part you evolve language, the other remain compatible with the previous version. This is what mitigates the issue with a big code base, too large for testing. I’ll return to the last question, that was about the reasons for changing: A reason for changing is discontinuing, sometimes there’s no other way, even if the application is stable. For example, with Python, the language stopped receiving maintenance, it ends up not being purely an issue of being able to add new features, but also an issue of not receiving any patch if they find a security flaw in this interpreter version, and you end up having no choice but to update. Back to the challenges, if the application is quite stable, it's hard convincing yourself that it’s worthwhile to update just to get a new feature, when this could mean losing application stability. If it’s a new feature that helps you perform maintenance and an application that has just been started or is riddled with bugs, it’s worth it. Theoretically, through doing this, the bug rate will get lower with time. Having a large application makes it harder, though it could be done gradually. When frameworks have drastic updates, they provide a migrating tool, there are also migrating guides, but preferably, an automated migration tool helps a lot. It’s a challenge if there are retrocompatibility issues, especially if they’re not algorithmically soluble. For example, from Python 2 to Python 3, they provided a migration tool, and there were changes like: In Python 2, print was a keyword, and in Python 3, a function, you could replace all print, space, anything for a print, open parenthesis, that same thing. It was algorithmical to do it. You could make a tool, even if the language update doesn't provide it, you could write it yourself and be quite confident with the results. If not, you’ll depend a lot on automated tests and this is another challenge. If your application has low test coverage, the previous challenges are amplified, and if you have a good test coverage, you can rest assured that it will be possible to identify where an issue is, as long as you run a series of tests on the migration.</t>
   </si>
   <si>
     <t>Being able to perform a gradual migration is a good thing: in one part you evolve language, the other remain compatible with the previous version. This is what mitigates the issue with a big code base, too large for testing.</t>
@@ -5208,7 +5208,7 @@
         <v>272</v>
       </c>
       <c r="C136" t="s">
-        <v>273</v>
+        <v>112</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -5219,10 +5219,10 @@
         <v>266</v>
       </c>
       <c r="B137" t="s">
+        <v>273</v>
+      </c>
+      <c r="C137" t="s">
         <v>274</v>
-      </c>
-      <c r="C137" t="s">
-        <v>112</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -5600,7 +5600,7 @@
         <v>319</v>
       </c>
       <c r="C164" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -5628,7 +5628,7 @@
         <v>321</v>
       </c>
       <c r="C166" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D166" t="s">
         <v>322</v>
@@ -5796,7 +5796,7 @@
         <v>340</v>
       </c>
       <c r="C178" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -5908,7 +5908,7 @@
         <v>351</v>
       </c>
       <c r="C186" t="s">
-        <v>352</v>
+        <v>112</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -5919,10 +5919,10 @@
         <v>337</v>
       </c>
       <c r="B187" t="s">
+        <v>352</v>
+      </c>
+      <c r="C187" t="s">
         <v>353</v>
-      </c>
-      <c r="C187" t="s">
-        <v>112</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>

--- a/quotations.xlsx
+++ b/quotations.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="873">
   <si>
     <t>document</t>
   </si>
@@ -893,13 +893,10 @@
     <t>For example: now, with the new Java versions, you write much less code; you abandon those more primitive algorithms, like doing algorithms to go through collections to find a certain element and make a return from it.</t>
   </si>
   <si>
-    <t>Python has gone through an evolutionary process, which is why, for many years, you had two versions of Python, the 2.7 x and the version 3. We even used to joke that Python has lost a few users because of that; thanks to Data Science, it has become the language it is nowadays: Machine Learning, Data Science, etc. But it has always been an excellent general-purpose language, including for web purposes, so the language evolution for software evolution is crucial. I was able to keep up with this type of evolution in several languages. Scala pushed Java to improvement, C# also pushed Java to improvement because Java fell behind, they saw how losing that thread of evolution could have an impact on the business</t>
-  </si>
-  <si>
     <t>Python has gone through an evolutionary process, which is why, for many years, you had two versions of Python, the 2.7 x and the version 3. We even used to joke that Python has lost a few users because of that; thanks to Data Science, it has become the language it is nowadays: Machine Learning, Data Science, etc. But it has always been an excellent general-purpose language, including for web purposes, so the language evolution for software evolution is crucial. I was able to keep up with this type of evolution in several languages. Scala pushed Java to improvement, C# also pushed Java to improvement because Java fell behind, they saw how losing that thread of evolution could have an impact on the business.</t>
   </si>
   <si>
-    <t>Programming language migration</t>
+    <t>Programming language migration, HR</t>
   </si>
   <si>
     <t>One of the most important aspects of evolving code, as the language evolves, is the need for migrating. One notorious language for giving developers headaches because of its ways of evolving is Scala. Its philosophy is: whatever becomes deprecated today, tomorrow will be lost. Code becomes unusable from one version to another, and the cost associated with leaving your code behind by two or three versions of the language is very high, both in time and energy spent in updating it. As a developer, it is very important to your day-to-day work to follow along with the language evolution, because it diminishes the cost of migrating an old codebase, which is hard to deal with, and saves you time down the road. Furthermore, it improves performance, since languages evolve in many aspects. Think about Ruby. From version 2.0 to version 3.0, it took an important step in improving performance. I went to a lecture by Koichi Sasada, who rewrote the entire garbage collector. He managed to make the garbage collector work three times faster, even though he said the goal was to make it ten times faster. Anyway, increasing its performance was an important improvement regarding its competitors, other faster and interpreted and compiled languages, like Python, Java, and C#. It is critically important that you are evolving your codebase as languages evolve so that you get new features, performance gains, security bug fixes, and avoid the trauma of migration.</t>
@@ -1042,6 +1039,9 @@
     <t>We have this application in Python 2.7, that we won’t even migrate, as it’s too obsolete. We’re making a new one to replace it, this time in Kotlin, it’s not in Python anymore.</t>
   </si>
   <si>
+    <t>Programming language migration</t>
+  </si>
+  <si>
     <t>When a new Kotlin version launches, we update immediately, because if you go, “I don’t have time now”, you’ll never have time, and the longer it takes, the worse it gets. Especially in those newer languages, that are coming with components like null safety, better typing and IDE integration, it spares a lot of trouble.</t>
   </si>
   <si>
@@ -1136,13 +1136,13 @@
     <t>Some of these languages that have wasted a lot of time on retrocompatibility, like JavaScript or PHP, are languages that pile up workarounds on language semantics with time. These changes that aim to make language simpler to understand, to remember, consequently make it harder to confuse and make a mistake, are also changes that make me want to evolve.</t>
   </si>
   <si>
+    <t>I think the main challenge is the code base size. If your code base is big, you may need to test a lot of code. I’ll number it: code base size, application stability. If you have a quite stable application, even if it uses a previous version of the language, it’s tough to pay the price of having to revalidate everything that was in that application.</t>
+  </si>
+  <si>
+    <t>Project complexity might hinder SCR efforts, Relevance of regression/automated testing, SCR requires careful planning, Analyse costs/benefits before rejuvenate</t>
+  </si>
+  <si>
     <t>I think the main challenge is the code base size. If your code base is big, you may need to test a lot of code. I’ll number it: code base size, application stability. If you have a quite stable application, even if it uses a previous version of the language, it’s tough to pay the price of having to revalidate everything that was in that application. Being able to perform a gradual migration is a good thing: in one part you evolve language, the other remain compatible with the previous version. This is what mitigates the issue with a big code base, too large for testing. I’ll return to the last question, that was about the reasons for changing: A reason for changing is discontinuing, sometimes there’s no other way, even if the application is stable. For example, with Python, the language stopped receiving maintenance, it ends up not being purely an issue of being able to add new features, but also an issue of not receiving any patch if they find a security flaw in this interpreter version, and you end up having no choice but to update. Back to the challenges, if the application is quite stable, it's hard convincing yourself that it’s worthwhile to update just to get a new feature, when this could mean losing application stability. If it’s a new feature that helps you perform maintenance and an application that has just been started or is riddled with bugs, it’s worth it. Theoretically, through doing this, the bug rate will get lower with time. Having a large application makes it harder, though it could be done gradually. When frameworks have drastic updates, they provide a migrating tool, there are also migrating guides, but preferably, an automated migration tool helps a lot. It’s a challenge if there are retrocompatibility issues, especially if they’re not algorithmically soluble. For example, from Python 2 to Python 3, they provided a migration tool, and there were changes like: In Python 2, print was a keyword, and in Python 3, a function, you could replace all print, space, anything for a print, open parenthesis, that same thing. It was algorithmical to do it. You could make a tool, even if the language update doesn't provide it, you could write it yourself and be quite confident with the results. If not, you’ll depend a lot on automated tests and this is another challenge. If your application has low test coverage, the previous challenges are amplified, and if you have a good test coverage, you can rest assured that it will be possible to identify where an issue is, as long as you run a series of tests on the migration.</t>
-  </si>
-  <si>
-    <t>I think the main challenge is the code base size. If your code base is big, you may need to test a lot of code. I’ll number it: code base size, application stability. If you have a quite stable application, even if it uses a previous version of the language, it’s tough to pay the price of having to revalidate everything that was in that application.</t>
-  </si>
-  <si>
-    <t>Project complexity might hinder SCR efforts, Relevance of regression/automated testing, SCR requires careful planning, Analyse costs/benefits before rejuvenate</t>
   </si>
   <si>
     <t>Being able to perform a gradual migration is a good thing: in one part you evolve language, the other remain compatible with the previous version. This is what mitigates the issue with a big code base, too large for testing.</t>
@@ -1277,10 +1277,10 @@
     <t>Language evolution might introduce breaking changes</t>
   </si>
   <si>
+    <t>In my opinion, it depends on some factors: One of them is the possibility of altering your code. In the case of this company’s main project, it is impossible, unfortunately. But if it’s not, I’d say it’s pretty nice, considering all the benefits that other versions of the language, such as Java, can bring about.</t>
+  </si>
+  <si>
     <t>In my opinion, it depends on some factors: One of them is the possibility of altering your code. In the case of this company’s main project, it is impossible, unfortunately. But if it’s not, I’d say it’s pretty nice, considering all the benefits that other versions of the language, such as Java, can bring about. For example, in Java 8, it included private resources, that is really handy when you’re making any requisitions to the database, as you can declare the transaction as well as the revert statement, that’s generated precisely so you can interact with the database inside a field of the catch, try block, and will automatically close the transaction as well as the revert statement. So, it ends up removing this memory that you always needed to have, in order to close the transaction and statement. This results in improvements in the code reading itself, legibility, as well as the fact that you will make less mistakes. Same thing with lambda expressions, from Java 8, that in my opinion, help a lot in simplifying code. But I also think that it depends, as there are new versions, for example Java 9 itself, or higher, these versions don’t add anything that makes evolving code mandatory, as of this new version. In Java 9’s case, that adds the modules, for example, you’d need to migrate your code from Java 8 to 9. And honestly, what was added in Java 9 is not anything that would necessarily make you migrate to use this new feature. In the modules’ case. It wouldn’t be enough to just set Java 9 as the main language. You’d need to perform a small migration to make it work with Java 9. In my opinion, it depends a lot on the project, the project time and also the project size itself. If the project is too large, unfortunately in many cases, in my experience, it’s not very easy for you to migrate from Java 7 to Java 10. It also depends a lot on what was added in the new version. Now, I think it’s interesting, in case you’re migrating to a new version, to migrate to one that will be long term supported. This way, you can guarantee it for the next 10 years, for example. I don’t know if it will be 10 years, but you will continue to have support for this version. So, if you migrate, you’d need to migrate to the next LTS version. That’s another thing: you need to see that no framework that’s necessary for it to work, not crash, the size that’ll be necessary for the job. There are many factors that need to be considered. From an academic point of view, you always think it’s nice to be updated with the versions, especially the LTS ones.</t>
-  </si>
-  <si>
-    <t>In my opinion, it depends on some factors: One of them is the possibility of altering your code. In the case of this company’s main project, it is impossible, unfortunately. But if it’s not, I’d say it’s pretty nice, considering all the benefits that other versions of the language, such as Java, can bring about.</t>
   </si>
   <si>
     <t>For example, in Java 8, it included private resources, that is really handy when you’re making any requisitions to the database, as you can declare the transaction as well as the revert statement, that’s generated precisely so you can interact with the database inside a field of the catch, try block, and will automatically close the transaction as well as the revert statement. So, it ends up removing this memory that you always needed to have, in order to close the transaction and statement. This results in improvements in the code reading itself, legibility, as well as the fact that you will make less mistakes.</t>
@@ -1528,14 +1528,14 @@
     <t>Well, in the IDE, with Eclipse, I generally use those Eclipse refactorings, but they are tangent to code structure. I don’t recall using any type of refactoring to evolve a code from one language version to another. I’ve used it a lot to perform refactoring, rename variables, extract methods, extract variables. But they are internal structure refactorings, not language ones, meant to evolve that project to a new language. Every time we needed to evolve a project to a new language, it was by hand.</t>
   </si>
   <si>
-    <t>Well, as I’ve already worked on less critical systems, and more critical ones, in this critical system it had to be done by hand, because you need to have criteria to evaluate whether that will cause a problem in runtime. That being said, we wouldn’t use any tools for this system anyways, and this was C++ and C. But these Java ones are generally less critical, even if they have an issue, it won’t lead to a tragic event, so to speak. It could be used in those Java systems, but I think we’d rather not use it, as sometimes you can see that it wouldn’t adapt well to a given case, but I also think that it may be a lack of practice in using those tools. Maybe it would be possible if the tool was more widespread, as people who work with Java have more flexibility to adopt these code generation, conversion tools. I think that it’s much better using it in a Java environment, though it wasn’t common practice where I worked, here in Brasilia.</t>
-  </si>
-  <si>
     <t>Well, as I’ve already worked on less critical systems, and more critical ones, in this critical system it had to be done by hand, because you need to have criteria to evaluate whether that will cause a problem in runtime.</t>
   </si>
   <si>
     <t xml:space="preserve">For critical systems its highly recommended to avoid automated tools to change the code directly.
 For non critical systems automated tools may be used to directly change the code.</t>
+  </si>
+  <si>
+    <t>Well, as I’ve already worked on less critical systems, and more critical ones, in this critical system it had to be done by hand, because you need to have criteria to evaluate whether that will cause a problem in runtime. That being said, we wouldn’t use any tools for this system anyways, and this was C++ and C. But these Java ones are generally less critical, even if they have an issue, it won’t lead to a tragic event, so to speak. It could be used in those Java systems, but I think we’d rather not use it, as sometimes you can see that it wouldn’t adapt well to a given case, but I also think that it may be a lack of practice in using those tools. Maybe it would be possible if the tool was more widespread, as people who work with Java have more flexibility to adopt these code generation, conversion tools. I think that it’s much better using it in a Java environment, though it wasn’t common practice where I worked, here in Brasilia.</t>
   </si>
   <si>
     <t>Well, today I struggle to follow it, as there are many versions, and you need to write code for it, perform tests, do a lot of stuff, so nowadays we don’t really have time to keep up with this technical part of language evolution. At least where I worked, few teams engaged in this, specifically. There’s a lot to do instead of assigning someone to look out for code evolving opportunities, it’s not common. So that’s why I have a hard time doing this. You get a version now, then six months to one year later, there’s a new one already. Keeping up with evolution is really hard. When the versions were released on a 4, 5-year basis, it was better. But now, that it’s yearly, or even twice a year, it’s just so hard. But there are also languages that don’t change per se, what really changes is the compiler. When it’s just the compiler, or interpreter, we can follow more easily, but when it’s the language itself, it’s harder to follow.</t>
@@ -1813,7 +1813,7 @@
 It's pretty much in this line, using JavaScript as an example. In React, I started developing the project and it was still done with classes. And then you had to bind everything, it was a totally different structure. And then came a version of React 9, I confess I don't remember which one it was. But they introduced Arrow Functions, everything became hooks in the system, everything became a function. And then I had to do this process of putting a part of the code, it wasn't everything. I usually took specific parts of the code to understand what was different, and from there I replicated it in other places. So it was more of a way to understand the changes between the versions, and from there I did the migration. I didn't use it as a migration tool, that is, I didn't put all the code there, it migrated and I copied it. It was more of a way to understand the specificities of each version.</t>
   </si>
   <si>
-    <t>Using LLMs to understand language evolution</t>
+    <t>LLM-based support for source code rejuvenation</t>
   </si>
   <si>
     <t>Yes, for sure. As I mentioned, I had to do a version migration process in a project with React. And I had to do a migration for each of the libs, from the one I was using to the most current one. So it was a lot of work, and I imagine that if I had a tool that would help me with that, I would definitely use it.</t>
@@ -1912,9 +1912,6 @@
 Because it's used to train.</t>
   </si>
   <si>
-    <t>Fear of exposing confidential code to AI tools, Limited trust in AI for complex development work, Developer expertise mediates the impact of LLMs on code evolution</t>
-  </si>
-  <si>
     <t xml:space="preserve">Exactly. But, in short, AI is good, but it has to evolve a lot. And Junior shouldn't use it.
 I've seen a lot of Junior who doesn't know how to code anymore.
 [Speaker 2]
@@ -1929,18 +1926,12 @@
 But most of the time, what's going to happen? If the guy delivered in that development environment, there's a little bit of data, it's something very calm, something good, it's going to work. In a few months, a few weeks, or even when the production goes up soon, it's going to go bad and you're going to have to patch it up.</t>
   </si>
   <si>
-    <t>Fear of overreliance inhibiting foundational skill development</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hmm. So, interesting, man. In that respect, I think it has something to do with the AI itself, right?
 AI is something very interesting, but I think it's starting to get better now, for training itself, right? With DeepSeek and so on, right? There are new hardwares that are coming out now to make it cheaper to train, but there's a big deficiency in something specific.
 Most of it is generic. And generic things, they will never reach the same performance as something that is specialized in itself. So, if you research this aspect of AI and make improvements in code and evolution of the language, cool, but specify a language first.
 In this case, too. Don't try to do something generic and make an upgrade, because the chance of failure will be great.</t>
   </si>
   <si>
-    <t>Perceived low reliability of LLM-generated output</t>
-  </si>
-  <si>
     <t>28-interview-translation.docx</t>
   </si>
   <si>
@@ -1965,7 +1956,7 @@
     <t>I see it with good eyes. Nowadays I don't usually use them, it's very rare to be using any of them. But because sometimes when I tried to use them, they brought me results that, when I really went to implement, I had to change a lot of things, so I prefer to do it manually. But I imagine that in the near future they will be part of the development. Even more than they are today.</t>
   </si>
   <si>
-    <t>Perceived low reliability of LLM-generated output, Manual SCR effort</t>
+    <t>Manual SCR effort, LLM-based support for source code rejuvenation</t>
   </si>
   <si>
     <t xml:space="preserve">At the moment I'm not using it in any way. And at work, I particularly don't know anyone who uses it, no. At least not that they speak openly about using it.
@@ -1973,9 +1964,6 @@
 Do you think it would be a problem, for example, within the company you work for, to use an LLM to support you in implementation?
 [Speaker 2]
 Well, the code and bank data are confidential, so I think there may be a privacy problem with regards to the data, since all these LLMs collect it. So I think there could be a problem, yes.</t>
-  </si>
-  <si>
-    <t>Fear of exposing confidential code to AI tools</t>
   </si>
   <si>
     <t>The participant links LLM use to potential confidentiality breaches, indicating that data governance concerns can constrain adoption regardless of perceived technical benefits.</t>
@@ -2051,7 +2039,7 @@
 We get suggestions on how to improve performance, but I'm still very fond of legibility, and nowadays the code created, either by IA or IDE, we still need to improve it, to make it a little more legible, a little more like us, you know?</t>
   </si>
   <si>
-    <t>Human-curated AI-generated code, Lack of trust in programming transformation tools</t>
+    <t>Lack of trust in programming transformation tools, LLM-based support for source code rejuvenation</t>
   </si>
   <si>
     <t>Use of generative AI tools to draft new code that developers subsequently revise, adapt, and align with team readability and design expectations, rather than adopting AI output verbatim.</t>
@@ -2064,24 +2052,15 @@
 Like, update this code for me.</t>
   </si>
   <si>
-    <t>Using LLMs to understand legacy code</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yes, maybe because of my age, I'm a little older, I'm almost 40, 37. So I'm used to breaking my head. That's the standard I knew.
 But the youngest people on the team, I see that they trust it totally. Like, go there, create it, do it. And there's no problem.
 I'm the one who's more likely to use it and still have the human intervention in this type of coding.</t>
   </si>
   <si>
-    <t>Experience-shaped trust in AI tools</t>
-  </si>
-  <si>
     <t>Differences in how developers rely on LLMs based on prior experience, with more experienced developers maintaining stronger human oversight while newer developers show higher trust and delegation.</t>
   </si>
   <si>
     <t>Dude, the impact is being absurd. In short, I'll explain this better. But in short, a developer who uses LLMs to develop produces the equivalent of three developers without LLMs. Like, in terms of functionality, amount of code, quality of code. So today the impact is, we need fewer developers to do the same amount as they do. What would you do with two, three? In our team, it was like that. The amount of tickets solved with LLM increased the speed a lot.</t>
-  </si>
-  <si>
-    <t>LLM-driven productivity gains</t>
   </si>
   <si>
     <t xml:space="preserve">Let me think here. About... To conclude, I would like to address the use of LLMs and the generational trends that are currently popular and widely discussed.
@@ -2097,7 +2076,7 @@
 We're just going to use the tools we have in a better way.</t>
   </si>
   <si>
-    <t>HR, LLMs enabling role shift from manual implementation to business-focused orchestration</t>
+    <t>HR, LLM-based support for source code rejuvenation</t>
   </si>
   <si>
     <t>The participant frames LLMs (together with cloud and CI/CD automation) as reducing manual “structural” work (tests, pipeline checks, deploy, environment creation), enabling perceived improvements in code and test quality. This shifts the developer’s role toward a consultant/orchestrator who intervenes punctually and concentrates on business logic and optimization. The human remains positioned as the “intelligence layer” over automated execution, reinforcing a narrative of augmentation rather than replacement.</t>
@@ -3301,7 +3280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D546"/>
+  <dimension ref="A1:D545"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -5208,7 +5187,7 @@
         <v>272</v>
       </c>
       <c r="C136" t="s">
-        <v>112</v>
+        <v>273</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -5219,10 +5198,10 @@
         <v>266</v>
       </c>
       <c r="B137" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C137" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -5233,10 +5212,10 @@
         <v>266</v>
       </c>
       <c r="B138" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C138" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -5247,10 +5226,10 @@
         <v>266</v>
       </c>
       <c r="B139" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C139" t="s">
-        <v>278</v>
+        <v>217</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -5264,7 +5243,7 @@
         <v>279</v>
       </c>
       <c r="C140" t="s">
-        <v>217</v>
+        <v>280</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -5275,10 +5254,10 @@
         <v>266</v>
       </c>
       <c r="B141" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C141" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -5289,10 +5268,10 @@
         <v>266</v>
       </c>
       <c r="B142" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C142" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -5303,10 +5282,10 @@
         <v>266</v>
       </c>
       <c r="B143" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C143" t="s">
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -5320,7 +5299,7 @@
         <v>286</v>
       </c>
       <c r="C144" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -5331,10 +5310,10 @@
         <v>266</v>
       </c>
       <c r="B145" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C145" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -5348,7 +5327,7 @@
         <v>289</v>
       </c>
       <c r="C146" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -5376,7 +5355,7 @@
         <v>291</v>
       </c>
       <c r="C148" t="s">
-        <v>265</v>
+        <v>46</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -5390,7 +5369,7 @@
         <v>292</v>
       </c>
       <c r="C149" t="s">
-        <v>46</v>
+        <v>293</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -5401,10 +5380,10 @@
         <v>266</v>
       </c>
       <c r="B150" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C150" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -5412,13 +5391,13 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="B151" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C151" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -5426,13 +5405,13 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B152" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C152" t="s">
-        <v>299</v>
+        <v>101</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -5440,13 +5419,13 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B153" t="s">
         <v>300</v>
       </c>
       <c r="C153" t="s">
-        <v>101</v>
+        <v>301</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -5454,41 +5433,41 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B154" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C154" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="D154" t="s">
-        <v>7</v>
+        <v>303</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B155" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C155" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="D155" t="s">
-        <v>304</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B156" t="s">
         <v>305</v>
       </c>
       <c r="C156" t="s">
-        <v>246</v>
+        <v>306</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -5496,13 +5475,13 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B157" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C157" t="s">
-        <v>307</v>
+        <v>65</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -5510,13 +5489,13 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B158" t="s">
         <v>308</v>
       </c>
       <c r="C158" t="s">
-        <v>65</v>
+        <v>309</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -5524,13 +5503,13 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="B159" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C159" t="s">
-        <v>310</v>
+        <v>158</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -5538,13 +5517,13 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B160" t="s">
         <v>312</v>
       </c>
       <c r="C160" t="s">
-        <v>158</v>
+        <v>313</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -5552,13 +5531,13 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B161" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C161" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -5566,13 +5545,13 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B162" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C162" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -5580,13 +5559,13 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B163" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C163" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -5594,13 +5573,13 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B164" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C164" t="s">
-        <v>274</v>
+        <v>204</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -5608,41 +5587,41 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B165" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C165" t="s">
-        <v>204</v>
+        <v>319</v>
       </c>
       <c r="D165" t="s">
-        <v>7</v>
+        <v>322</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B166" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C166" t="s">
-        <v>274</v>
+        <v>324</v>
       </c>
       <c r="D166" t="s">
-        <v>322</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B167" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C167" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -5650,13 +5629,13 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B168" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C168" t="s">
-        <v>326</v>
+        <v>115</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -5664,13 +5643,13 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B169" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C169" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -5678,13 +5657,13 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B170" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C170" t="s">
-        <v>87</v>
+        <v>330</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -5692,13 +5671,13 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B171" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C171" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -5706,13 +5685,13 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B172" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C172" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -5720,13 +5699,13 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B173" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C173" t="s">
-        <v>334</v>
+        <v>246</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -5734,13 +5713,13 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B174" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C174" t="s">
-        <v>246</v>
+        <v>334</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -5748,13 +5727,13 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="B175" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C175" t="s">
-        <v>334</v>
+        <v>112</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -5765,10 +5744,10 @@
         <v>337</v>
       </c>
       <c r="B176" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C176" t="s">
-        <v>112</v>
+        <v>330</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -5779,10 +5758,10 @@
         <v>337</v>
       </c>
       <c r="B177" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C177" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -5793,13 +5772,13 @@
         <v>337</v>
       </c>
       <c r="B178" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C178" t="s">
-        <v>274</v>
+        <v>158</v>
       </c>
       <c r="D178" t="s">
-        <v>7</v>
+        <v>342</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -5807,13 +5786,13 @@
         <v>337</v>
       </c>
       <c r="B179" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C179" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="D179" t="s">
-        <v>342</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -5821,10 +5800,10 @@
         <v>337</v>
       </c>
       <c r="B180" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C180" t="s">
-        <v>179</v>
+        <v>345</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -5835,10 +5814,10 @@
         <v>337</v>
       </c>
       <c r="B181" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C181" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -5849,10 +5828,10 @@
         <v>337</v>
       </c>
       <c r="B182" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C182" t="s">
-        <v>347</v>
+        <v>217</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -5863,10 +5842,10 @@
         <v>337</v>
       </c>
       <c r="B183" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C183" t="s">
-        <v>217</v>
+        <v>99</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -5877,10 +5856,10 @@
         <v>337</v>
       </c>
       <c r="B184" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C184" t="s">
-        <v>99</v>
+        <v>332</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -5891,10 +5870,10 @@
         <v>337</v>
       </c>
       <c r="B185" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C185" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -5905,7 +5884,7 @@
         <v>337</v>
       </c>
       <c r="B186" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C186" t="s">
         <v>112</v>
@@ -5919,10 +5898,10 @@
         <v>337</v>
       </c>
       <c r="B187" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C187" t="s">
-        <v>353</v>
+        <v>25</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -5933,10 +5912,10 @@
         <v>337</v>
       </c>
       <c r="B188" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C188" t="s">
-        <v>25</v>
+        <v>330</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -5947,10 +5926,10 @@
         <v>337</v>
       </c>
       <c r="B189" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C189" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -5961,10 +5940,10 @@
         <v>337</v>
       </c>
       <c r="B190" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C190" t="s">
-        <v>357</v>
+        <v>25</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -5975,10 +5954,10 @@
         <v>337</v>
       </c>
       <c r="B191" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C191" t="s">
-        <v>25</v>
+        <v>334</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -5989,10 +5968,10 @@
         <v>337</v>
       </c>
       <c r="B192" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C192" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -6003,10 +5982,10 @@
         <v>337</v>
       </c>
       <c r="B193" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C193" t="s">
-        <v>332</v>
+        <v>29</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -6017,10 +5996,10 @@
         <v>337</v>
       </c>
       <c r="B194" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C194" t="s">
-        <v>29</v>
+        <v>246</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -6031,10 +6010,10 @@
         <v>337</v>
       </c>
       <c r="B195" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C195" t="s">
-        <v>246</v>
+        <v>334</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -6045,10 +6024,10 @@
         <v>337</v>
       </c>
       <c r="B196" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C196" t="s">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -6056,13 +6035,13 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="B197" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C197" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -6073,10 +6052,10 @@
         <v>366</v>
       </c>
       <c r="B198" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C198" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -6087,10 +6066,10 @@
         <v>366</v>
       </c>
       <c r="B199" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C199" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -6101,10 +6080,10 @@
         <v>366</v>
       </c>
       <c r="B200" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C200" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -6115,10 +6094,10 @@
         <v>366</v>
       </c>
       <c r="B201" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C201" t="s">
-        <v>374</v>
+        <v>16</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -6129,10 +6108,10 @@
         <v>366</v>
       </c>
       <c r="B202" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C202" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -6140,13 +6119,13 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="B203" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C203" t="s">
-        <v>158</v>
+        <v>379</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -6157,10 +6136,10 @@
         <v>377</v>
       </c>
       <c r="B204" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C204" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -6171,10 +6150,10 @@
         <v>377</v>
       </c>
       <c r="B205" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C205" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -6185,10 +6164,10 @@
         <v>377</v>
       </c>
       <c r="B206" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C206" t="s">
-        <v>383</v>
+        <v>326</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -6199,10 +6178,10 @@
         <v>377</v>
       </c>
       <c r="B207" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C207" t="s">
-        <v>326</v>
+        <v>386</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -6213,10 +6192,10 @@
         <v>377</v>
       </c>
       <c r="B208" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C208" t="s">
-        <v>386</v>
+        <v>97</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -6227,10 +6206,10 @@
         <v>377</v>
       </c>
       <c r="B209" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C209" t="s">
-        <v>97</v>
+        <v>389</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -6241,10 +6220,10 @@
         <v>377</v>
       </c>
       <c r="B210" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C210" t="s">
-        <v>389</v>
+        <v>246</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -6255,7 +6234,7 @@
         <v>377</v>
       </c>
       <c r="B211" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C211" t="s">
         <v>246</v>
@@ -6269,10 +6248,10 @@
         <v>377</v>
       </c>
       <c r="B212" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C212" t="s">
-        <v>246</v>
+        <v>112</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -6280,13 +6259,13 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="B213" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C213" t="s">
-        <v>112</v>
+        <v>202</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -6297,10 +6276,10 @@
         <v>393</v>
       </c>
       <c r="B214" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C214" t="s">
-        <v>202</v>
+        <v>396</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -6311,10 +6290,10 @@
         <v>393</v>
       </c>
       <c r="B215" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C215" t="s">
-        <v>396</v>
+        <v>345</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -6325,7 +6304,7 @@
         <v>393</v>
       </c>
       <c r="B216" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C216" t="s">
         <v>112</v>
@@ -6339,10 +6318,10 @@
         <v>393</v>
       </c>
       <c r="B217" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C217" t="s">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -6353,10 +6332,10 @@
         <v>393</v>
       </c>
       <c r="B218" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C218" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -6367,10 +6346,10 @@
         <v>393</v>
       </c>
       <c r="B219" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C219" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -6381,10 +6360,10 @@
         <v>393</v>
       </c>
       <c r="B220" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C220" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -6395,10 +6374,10 @@
         <v>393</v>
       </c>
       <c r="B221" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C221" t="s">
-        <v>406</v>
+        <v>202</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -6409,10 +6388,10 @@
         <v>393</v>
       </c>
       <c r="B222" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C222" t="s">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -6423,10 +6402,10 @@
         <v>393</v>
       </c>
       <c r="B223" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C223" t="s">
-        <v>152</v>
+        <v>410</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -6437,13 +6416,13 @@
         <v>393</v>
       </c>
       <c r="B224" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C224" t="s">
-        <v>410</v>
+        <v>265</v>
       </c>
       <c r="D224" t="s">
-        <v>7</v>
+        <v>412</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -6451,13 +6430,13 @@
         <v>393</v>
       </c>
       <c r="B225" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C225" t="s">
-        <v>265</v>
+        <v>414</v>
       </c>
       <c r="D225" t="s">
-        <v>412</v>
+        <v>7</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -6465,7 +6444,7 @@
         <v>393</v>
       </c>
       <c r="B226" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C226" t="s">
         <v>414</v>
@@ -6479,10 +6458,10 @@
         <v>393</v>
       </c>
       <c r="B227" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C227" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -6493,10 +6472,10 @@
         <v>393</v>
       </c>
       <c r="B228" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C228" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -6507,10 +6486,10 @@
         <v>393</v>
       </c>
       <c r="B229" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C229" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -6518,13 +6497,13 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>393</v>
+        <v>422</v>
       </c>
       <c r="B230" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C230" t="s">
-        <v>421</v>
+        <v>326</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -6535,10 +6514,10 @@
         <v>422</v>
       </c>
       <c r="B231" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C231" t="s">
-        <v>326</v>
+        <v>425</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -6549,10 +6528,10 @@
         <v>422</v>
       </c>
       <c r="B232" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C232" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -6563,10 +6542,10 @@
         <v>422</v>
       </c>
       <c r="B233" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C233" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -6577,10 +6556,10 @@
         <v>422</v>
       </c>
       <c r="B234" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C234" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -6591,10 +6570,10 @@
         <v>422</v>
       </c>
       <c r="B235" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C235" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -6605,10 +6584,10 @@
         <v>422</v>
       </c>
       <c r="B236" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C236" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -6619,10 +6598,10 @@
         <v>422</v>
       </c>
       <c r="B237" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C237" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -6633,10 +6612,10 @@
         <v>422</v>
       </c>
       <c r="B238" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C238" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -6647,10 +6626,10 @@
         <v>422</v>
       </c>
       <c r="B239" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C239" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -6658,16 +6637,16 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="B240" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C240" t="s">
-        <v>441</v>
+        <v>101</v>
       </c>
       <c r="D240" t="s">
-        <v>7</v>
+        <v>444</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -6675,13 +6654,13 @@
         <v>442</v>
       </c>
       <c r="B241" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C241" t="s">
-        <v>101</v>
+        <v>446</v>
       </c>
       <c r="D241" t="s">
-        <v>444</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
@@ -6689,10 +6668,10 @@
         <v>442</v>
       </c>
       <c r="B242" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C242" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -6703,10 +6682,10 @@
         <v>442</v>
       </c>
       <c r="B243" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C243" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -6717,10 +6696,10 @@
         <v>442</v>
       </c>
       <c r="B244" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C244" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -6728,13 +6707,13 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="B245" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C245" t="s">
-        <v>452</v>
+        <v>217</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -6745,10 +6724,10 @@
         <v>453</v>
       </c>
       <c r="B246" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C246" t="s">
-        <v>217</v>
+        <v>456</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -6759,10 +6738,10 @@
         <v>453</v>
       </c>
       <c r="B247" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C247" t="s">
-        <v>456</v>
+        <v>345</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -6773,10 +6752,10 @@
         <v>453</v>
       </c>
       <c r="B248" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C248" t="s">
-        <v>345</v>
+        <v>224</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -6787,10 +6766,10 @@
         <v>453</v>
       </c>
       <c r="B249" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C249" t="s">
-        <v>224</v>
+        <v>460</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -6801,10 +6780,10 @@
         <v>453</v>
       </c>
       <c r="B250" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C250" t="s">
-        <v>460</v>
+        <v>406</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -6815,10 +6794,10 @@
         <v>453</v>
       </c>
       <c r="B251" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C251" t="s">
-        <v>406</v>
+        <v>463</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -6829,13 +6808,13 @@
         <v>453</v>
       </c>
       <c r="B252" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C252" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D252" t="s">
-        <v>7</v>
+        <v>466</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
@@ -6843,13 +6822,13 @@
         <v>453</v>
       </c>
       <c r="B253" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C253" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D253" t="s">
-        <v>466</v>
+        <v>7</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
@@ -6857,10 +6836,10 @@
         <v>453</v>
       </c>
       <c r="B254" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C254" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -6871,10 +6850,10 @@
         <v>453</v>
       </c>
       <c r="B255" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C255" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -6885,10 +6864,10 @@
         <v>453</v>
       </c>
       <c r="B256" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C256" t="s">
-        <v>452</v>
+        <v>217</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -6899,7 +6878,7 @@
         <v>453</v>
       </c>
       <c r="B257" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C257" t="s">
         <v>217</v>
@@ -6913,10 +6892,10 @@
         <v>453</v>
       </c>
       <c r="B258" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C258" t="s">
-        <v>217</v>
+        <v>46</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -6927,7 +6906,7 @@
         <v>453</v>
       </c>
       <c r="B259" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C259" t="s">
         <v>46</v>
@@ -6941,13 +6920,13 @@
         <v>453</v>
       </c>
       <c r="B260" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C260" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D260" t="s">
-        <v>7</v>
+        <v>477</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
@@ -6955,7 +6934,7 @@
         <v>453</v>
       </c>
       <c r="B261" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C261" t="s">
         <v>46</v>
@@ -6969,13 +6948,13 @@
         <v>453</v>
       </c>
       <c r="B262" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C262" t="s">
-        <v>33</v>
+        <v>480</v>
       </c>
       <c r="D262" t="s">
-        <v>478</v>
+        <v>7</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -6983,10 +6962,10 @@
         <v>453</v>
       </c>
       <c r="B263" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C263" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -6997,10 +6976,10 @@
         <v>453</v>
       </c>
       <c r="B264" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C264" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -7011,13 +6990,13 @@
         <v>453</v>
       </c>
       <c r="B265" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C265" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D265" t="s">
-        <v>7</v>
+        <v>487</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -7025,13 +7004,13 @@
         <v>453</v>
       </c>
       <c r="B266" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C266" t="s">
-        <v>486</v>
+        <v>65</v>
       </c>
       <c r="D266" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -7039,13 +7018,13 @@
         <v>453</v>
       </c>
       <c r="B267" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C267" t="s">
-        <v>65</v>
+        <v>484</v>
       </c>
       <c r="D267" t="s">
-        <v>489</v>
+        <v>7</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -7056,7 +7035,7 @@
         <v>490</v>
       </c>
       <c r="C268" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -7067,10 +7046,10 @@
         <v>453</v>
       </c>
       <c r="B269" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C269" t="s">
-        <v>491</v>
+        <v>417</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -7081,10 +7060,10 @@
         <v>453</v>
       </c>
       <c r="B270" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C270" t="s">
-        <v>417</v>
+        <v>29</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -7095,10 +7074,10 @@
         <v>453</v>
       </c>
       <c r="B271" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C271" t="s">
-        <v>29</v>
+        <v>495</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -7109,10 +7088,10 @@
         <v>453</v>
       </c>
       <c r="B272" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C272" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -7123,10 +7102,10 @@
         <v>453</v>
       </c>
       <c r="B273" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C273" t="s">
-        <v>484</v>
+        <v>246</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -7134,13 +7113,13 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>453</v>
+        <v>498</v>
       </c>
       <c r="B274" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C274" t="s">
-        <v>246</v>
+        <v>500</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -7151,10 +7130,10 @@
         <v>498</v>
       </c>
       <c r="B275" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C275" t="s">
-        <v>500</v>
+        <v>103</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -7165,10 +7144,10 @@
         <v>498</v>
       </c>
       <c r="B276" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C276" t="s">
-        <v>103</v>
+        <v>503</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -7179,10 +7158,10 @@
         <v>498</v>
       </c>
       <c r="B277" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C277" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -7193,10 +7172,10 @@
         <v>498</v>
       </c>
       <c r="B278" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C278" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -7207,10 +7186,10 @@
         <v>498</v>
       </c>
       <c r="B279" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C279" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -7221,10 +7200,10 @@
         <v>498</v>
       </c>
       <c r="B280" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C280" t="s">
-        <v>509</v>
+        <v>103</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -7235,10 +7214,10 @@
         <v>498</v>
       </c>
       <c r="B281" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C281" t="s">
-        <v>103</v>
+        <v>512</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -7249,10 +7228,10 @@
         <v>498</v>
       </c>
       <c r="B282" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C282" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -7263,10 +7242,10 @@
         <v>498</v>
       </c>
       <c r="B283" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C283" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -7277,10 +7256,10 @@
         <v>498</v>
       </c>
       <c r="B284" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C284" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -7291,10 +7270,10 @@
         <v>498</v>
       </c>
       <c r="B285" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C285" t="s">
-        <v>518</v>
+        <v>103</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -7302,13 +7281,13 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>498</v>
+        <v>520</v>
       </c>
       <c r="B286" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C286" t="s">
-        <v>103</v>
+        <v>522</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -7319,10 +7298,10 @@
         <v>520</v>
       </c>
       <c r="B287" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C287" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -7333,10 +7312,10 @@
         <v>520</v>
       </c>
       <c r="B288" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C288" t="s">
-        <v>524</v>
+        <v>217</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -7347,10 +7326,10 @@
         <v>520</v>
       </c>
       <c r="B289" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C289" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -7361,10 +7340,10 @@
         <v>520</v>
       </c>
       <c r="B290" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C290" t="s">
-        <v>248</v>
+        <v>528</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -7375,10 +7354,10 @@
         <v>520</v>
       </c>
       <c r="B291" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C291" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -7389,10 +7368,10 @@
         <v>520</v>
       </c>
       <c r="B292" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C292" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -7403,10 +7382,10 @@
         <v>520</v>
       </c>
       <c r="B293" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C293" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -7417,10 +7396,10 @@
         <v>520</v>
       </c>
       <c r="B294" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C294" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -7431,10 +7410,10 @@
         <v>520</v>
       </c>
       <c r="B295" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C295" t="s">
-        <v>536</v>
+        <v>230</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -7445,10 +7424,10 @@
         <v>520</v>
       </c>
       <c r="B296" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C296" t="s">
-        <v>230</v>
+        <v>539</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -7459,10 +7438,10 @@
         <v>520</v>
       </c>
       <c r="B297" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C297" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -7473,10 +7452,10 @@
         <v>520</v>
       </c>
       <c r="B298" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C298" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -7484,13 +7463,13 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
       <c r="B299" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C299" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -7501,10 +7480,10 @@
         <v>544</v>
       </c>
       <c r="B300" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C300" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -7515,10 +7494,10 @@
         <v>544</v>
       </c>
       <c r="B301" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C301" t="s">
-        <v>548</v>
+        <v>406</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -7529,10 +7508,10 @@
         <v>544</v>
       </c>
       <c r="B302" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C302" t="s">
-        <v>406</v>
+        <v>217</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -7543,10 +7522,10 @@
         <v>544</v>
       </c>
       <c r="B303" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C303" t="s">
-        <v>217</v>
+        <v>332</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -7557,10 +7536,10 @@
         <v>544</v>
       </c>
       <c r="B304" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C304" t="s">
-        <v>332</v>
+        <v>99</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -7571,10 +7550,10 @@
         <v>544</v>
       </c>
       <c r="B305" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C305" t="s">
-        <v>99</v>
+        <v>554</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -7585,10 +7564,10 @@
         <v>544</v>
       </c>
       <c r="B306" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C306" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -7599,10 +7578,10 @@
         <v>544</v>
       </c>
       <c r="B307" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C307" t="s">
-        <v>556</v>
+        <v>101</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -7613,10 +7592,10 @@
         <v>544</v>
       </c>
       <c r="B308" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C308" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -7627,10 +7606,10 @@
         <v>544</v>
       </c>
       <c r="B309" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C309" t="s">
-        <v>79</v>
+        <v>452</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -7641,10 +7620,10 @@
         <v>544</v>
       </c>
       <c r="B310" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C310" t="s">
-        <v>452</v>
+        <v>561</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -7655,10 +7634,10 @@
         <v>544</v>
       </c>
       <c r="B311" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C311" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -7666,13 +7645,13 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>544</v>
+        <v>564</v>
       </c>
       <c r="B312" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C312" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -7683,10 +7662,10 @@
         <v>564</v>
       </c>
       <c r="B313" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C313" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -7697,10 +7676,10 @@
         <v>564</v>
       </c>
       <c r="B314" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C314" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -7711,10 +7690,10 @@
         <v>564</v>
       </c>
       <c r="B315" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C315" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -7725,10 +7704,10 @@
         <v>564</v>
       </c>
       <c r="B316" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C316" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -7739,10 +7718,10 @@
         <v>564</v>
       </c>
       <c r="B317" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C317" t="s">
-        <v>574</v>
+        <v>330</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -7753,10 +7732,10 @@
         <v>564</v>
       </c>
       <c r="B318" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C318" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -7767,10 +7746,10 @@
         <v>564</v>
       </c>
       <c r="B319" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C319" t="s">
-        <v>345</v>
+        <v>578</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -7781,10 +7760,10 @@
         <v>564</v>
       </c>
       <c r="B320" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C320" t="s">
-        <v>578</v>
+        <v>46</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -7795,10 +7774,10 @@
         <v>564</v>
       </c>
       <c r="B321" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C321" t="s">
-        <v>46</v>
+        <v>561</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -7809,10 +7788,10 @@
         <v>564</v>
       </c>
       <c r="B322" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C322" t="s">
-        <v>581</v>
+        <v>561</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -7826,7 +7805,7 @@
         <v>582</v>
       </c>
       <c r="C323" t="s">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -7834,13 +7813,13 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>564</v>
+        <v>583</v>
       </c>
       <c r="B324" t="s">
         <v>584</v>
       </c>
       <c r="C324" t="s">
-        <v>585</v>
+        <v>217</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -7848,13 +7827,13 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B325" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C325" t="s">
-        <v>217</v>
+        <v>21</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -7862,13 +7841,13 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
+        <v>583</v>
+      </c>
+      <c r="B326" t="s">
         <v>586</v>
       </c>
-      <c r="B326" t="s">
-        <v>588</v>
-      </c>
       <c r="C326" t="s">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -7876,13 +7855,13 @@
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B327" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C327" t="s">
-        <v>217</v>
+        <v>452</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -7890,13 +7869,13 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B328" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C328" t="s">
-        <v>452</v>
+        <v>65</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -7904,13 +7883,13 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B329" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C329" t="s">
-        <v>65</v>
+        <v>590</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -7918,21 +7897,21 @@
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B330" t="s">
+        <v>591</v>
+      </c>
+      <c r="C330" t="s">
+        <v>561</v>
+      </c>
+      <c r="D330" t="s">
         <v>592</v>
-      </c>
-      <c r="C330" t="s">
-        <v>593</v>
-      </c>
-      <c r="D330" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="B331" t="s">
         <v>594</v>
@@ -7941,18 +7920,18 @@
         <v>595</v>
       </c>
       <c r="D331" t="s">
-        <v>596</v>
+        <v>7</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
+        <v>593</v>
+      </c>
+      <c r="B332" t="s">
+        <v>596</v>
+      </c>
+      <c r="C332" t="s">
         <v>597</v>
-      </c>
-      <c r="B332" t="s">
-        <v>598</v>
-      </c>
-      <c r="C332" t="s">
-        <v>599</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -7960,13 +7939,13 @@
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B333" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C333" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -7974,13 +7953,13 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B334" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C334" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -7988,13 +7967,13 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B335" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C335" t="s">
-        <v>605</v>
+        <v>347</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -8002,13 +7981,13 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B336" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C336" t="s">
-        <v>347</v>
+        <v>604</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -8016,13 +7995,13 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B337" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C337" t="s">
-        <v>608</v>
+        <v>99</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -8030,13 +8009,13 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B338" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C338" t="s">
-        <v>99</v>
+        <v>607</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -8044,13 +8023,13 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B339" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C339" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -8058,13 +8037,13 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B340" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C340" t="s">
-        <v>613</v>
+        <v>25</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -8072,97 +8051,97 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B341" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C341" t="s">
-        <v>25</v>
+        <v>612</v>
       </c>
       <c r="D341" t="s">
-        <v>7</v>
+        <v>613</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B342" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C342" t="s">
-        <v>616</v>
+        <v>561</v>
       </c>
       <c r="D342" t="s">
-        <v>617</v>
+        <v>7</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B343" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C343" t="s">
-        <v>619</v>
+        <v>561</v>
       </c>
       <c r="D343" t="s">
-        <v>7</v>
+        <v>616</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B344" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C344" t="s">
-        <v>621</v>
+        <v>561</v>
       </c>
       <c r="D344" t="s">
-        <v>622</v>
+        <v>7</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B345" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C345" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="D345" t="s">
-        <v>7</v>
+        <v>620</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>597</v>
+        <v>621</v>
       </c>
       <c r="B346" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C346" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D346" t="s">
-        <v>627</v>
+        <v>7</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B347" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="C347" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -8170,13 +8149,13 @@
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B348" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C348" t="s">
-        <v>632</v>
+        <v>25</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -8184,10 +8163,10 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B349" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C349" t="s">
         <v>25</v>
@@ -8198,13 +8177,13 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
+        <v>621</v>
+      </c>
+      <c r="B350" t="s">
         <v>628</v>
       </c>
-      <c r="B350" t="s">
-        <v>634</v>
-      </c>
       <c r="C350" t="s">
-        <v>25</v>
+        <v>629</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -8212,13 +8191,13 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B351" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="C351" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -8226,13 +8205,13 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B352" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C352" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -8240,13 +8219,13 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B353" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C353" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -8254,13 +8233,13 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B354" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C354" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -8268,13 +8247,13 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B355" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="C355" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -8282,13 +8261,13 @@
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>628</v>
+        <v>638</v>
       </c>
       <c r="B356" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C356" t="s">
-        <v>644</v>
+        <v>625</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -8296,13 +8275,13 @@
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B357" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C357" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -8310,13 +8289,13 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B358" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C358" t="s">
-        <v>632</v>
+        <v>25</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -8324,13 +8303,13 @@
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B359" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C359" t="s">
-        <v>25</v>
+        <v>623</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -8338,13 +8317,13 @@
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B360" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C360" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -8352,13 +8331,13 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B361" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="C361" t="s">
-        <v>630</v>
+        <v>79</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -8366,13 +8345,13 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
+        <v>638</v>
+      </c>
+      <c r="B362" t="s">
         <v>645</v>
       </c>
-      <c r="B362" t="s">
-        <v>651</v>
-      </c>
       <c r="C362" t="s">
-        <v>79</v>
+        <v>623</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -8380,13 +8359,13 @@
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B363" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C363" t="s">
-        <v>630</v>
+        <v>79</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -8394,13 +8373,13 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B364" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C364" t="s">
-        <v>79</v>
+        <v>629</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -8408,13 +8387,13 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B365" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C365" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -8422,13 +8401,13 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B366" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C366" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -8436,13 +8415,13 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B367" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="C367" t="s">
-        <v>636</v>
+        <v>595</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -8450,13 +8429,13 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="B368" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C368" t="s">
-        <v>599</v>
+        <v>25</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -8464,13 +8443,13 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="B369" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C369" t="s">
-        <v>25</v>
+        <v>625</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -8478,13 +8457,13 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="B370" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C370" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -8492,13 +8471,13 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="B371" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="C371" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -8506,13 +8485,13 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="B372" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="C372" t="s">
-        <v>632</v>
+        <v>657</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -8520,13 +8499,13 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
+        <v>651</v>
+      </c>
+      <c r="B373" t="s">
         <v>658</v>
       </c>
-      <c r="B373" t="s">
-        <v>663</v>
-      </c>
       <c r="C373" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -8534,13 +8513,13 @@
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B374" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C374" t="s">
-        <v>666</v>
+        <v>152</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -8548,13 +8527,13 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B375" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="C375" t="s">
-        <v>152</v>
+        <v>663</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -8562,13 +8541,13 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B376" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="C376" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -8576,13 +8555,13 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B377" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C377" t="s">
-        <v>672</v>
+        <v>334</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -8590,13 +8569,13 @@
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
+        <v>660</v>
+      </c>
+      <c r="B378" t="s">
         <v>667</v>
       </c>
-      <c r="B378" t="s">
-        <v>673</v>
-      </c>
       <c r="C378" t="s">
-        <v>334</v>
+        <v>668</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -8604,13 +8583,13 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B379" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="C379" t="s">
-        <v>675</v>
+        <v>345</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -8618,13 +8597,13 @@
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B380" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="C380" t="s">
-        <v>345</v>
+        <v>101</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -8632,13 +8611,13 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B381" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="C381" t="s">
-        <v>101</v>
+        <v>468</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -8646,13 +8625,13 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B382" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="C382" t="s">
-        <v>468</v>
+        <v>217</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -8660,13 +8639,13 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B383" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="C383" t="s">
-        <v>217</v>
+        <v>334</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -8674,13 +8653,13 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B384" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="C384" t="s">
-        <v>334</v>
+        <v>675</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -8688,13 +8667,13 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B385" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="C385" t="s">
-        <v>682</v>
+        <v>202</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -8702,13 +8681,13 @@
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B386" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="C386" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -8716,13 +8695,13 @@
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B387" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="C387" t="s">
-        <v>248</v>
+        <v>679</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -8730,13 +8709,13 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B388" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="C388" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -8744,13 +8723,13 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B389" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="C389" t="s">
-        <v>688</v>
+        <v>543</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -8758,13 +8737,13 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B390" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="C390" t="s">
-        <v>543</v>
+        <v>265</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -8772,13 +8751,13 @@
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B391" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="C391" t="s">
-        <v>265</v>
+        <v>685</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -8786,13 +8765,13 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B392" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C392" t="s">
-        <v>692</v>
+        <v>158</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -8800,13 +8779,13 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B393" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C393" t="s">
-        <v>158</v>
+        <v>688</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -8814,13 +8793,13 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B394" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="C394" t="s">
-        <v>695</v>
+        <v>202</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -8828,13 +8807,13 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B395" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="C395" t="s">
-        <v>202</v>
+        <v>691</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -8842,13 +8821,13 @@
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B396" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C396" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -8856,13 +8835,13 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B397" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="C397" t="s">
-        <v>700</v>
+        <v>158</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -8870,10 +8849,10 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B398" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="C398" t="s">
         <v>158</v>
@@ -8884,13 +8863,13 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B399" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C399" t="s">
-        <v>158</v>
+        <v>697</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -8898,13 +8877,13 @@
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B400" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="C400" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -8912,13 +8891,13 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B401" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="C401" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -8926,13 +8905,13 @@
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B402" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="C402" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -8940,13 +8919,13 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B403" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="C403" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -8954,13 +8933,13 @@
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B404" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="C404" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -8968,13 +8947,13 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B405" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="C405" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -8982,13 +8961,13 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B406" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="C406" t="s">
-        <v>714</v>
+        <v>158</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -8996,10 +8975,10 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B407" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="C407" t="s">
         <v>158</v>
@@ -9010,13 +8989,13 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B408" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="C408" t="s">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -9024,10 +9003,10 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B409" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="C409" t="s">
         <v>202</v>
@@ -9038,13 +9017,13 @@
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B410" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="C410" t="s">
-        <v>202</v>
+        <v>546</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -9052,13 +9031,13 @@
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B411" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="C411" t="s">
-        <v>546</v>
+        <v>679</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -9066,13 +9045,13 @@
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B412" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="C412" t="s">
-        <v>686</v>
+        <v>716</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -9080,13 +9059,13 @@
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B413" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="C413" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -9094,13 +9073,13 @@
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B414" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="C414" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -9108,13 +9087,13 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B415" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="C415" t="s">
-        <v>725</v>
+        <v>334</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -9122,13 +9101,13 @@
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B416" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C416" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -9136,13 +9115,13 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B417" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C417" t="s">
-        <v>345</v>
+        <v>202</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -9150,10 +9129,10 @@
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B418" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="C418" t="s">
         <v>202</v>
@@ -9164,13 +9143,13 @@
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B419" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="C419" t="s">
-        <v>202</v>
+        <v>87</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -9178,13 +9157,13 @@
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B420" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C420" t="s">
-        <v>87</v>
+        <v>726</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -9192,13 +9171,13 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B421" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="C421" t="s">
-        <v>733</v>
+        <v>707</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -9206,13 +9185,13 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B422" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C422" t="s">
-        <v>714</v>
+        <v>202</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -9220,13 +9199,13 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B423" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="C423" t="s">
-        <v>202</v>
+        <v>730</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -9234,13 +9213,13 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B424" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C424" t="s">
-        <v>737</v>
+        <v>152</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -9248,13 +9227,13 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B425" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="C425" t="s">
-        <v>152</v>
+        <v>733</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -9262,13 +9241,13 @@
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B426" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="C426" t="s">
-        <v>740</v>
+        <v>217</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -9276,13 +9255,13 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B427" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="C427" t="s">
-        <v>217</v>
+        <v>703</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -9290,13 +9269,13 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B428" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="C428" t="s">
-        <v>710</v>
+        <v>737</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -9304,13 +9283,13 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B429" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C429" t="s">
-        <v>744</v>
+        <v>301</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -9318,13 +9297,13 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B430" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="C430" t="s">
-        <v>302</v>
+        <v>152</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -9332,13 +9311,13 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B431" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="C431" t="s">
-        <v>152</v>
+        <v>217</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -9346,13 +9325,13 @@
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B432" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="C432" t="s">
-        <v>217</v>
+        <v>152</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -9360,13 +9339,13 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B433" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="C433" t="s">
-        <v>152</v>
+        <v>743</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -9374,13 +9353,13 @@
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B434" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="C434" t="s">
-        <v>750</v>
+        <v>334</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -9388,13 +9367,13 @@
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B435" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="C435" t="s">
-        <v>334</v>
+        <v>718</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -9402,13 +9381,13 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B436" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="C436" t="s">
-        <v>725</v>
+        <v>345</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -9416,13 +9395,13 @@
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B437" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="C437" t="s">
-        <v>345</v>
+        <v>7</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -9430,13 +9409,13 @@
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B438" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="C438" t="s">
-        <v>7</v>
+        <v>217</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -9444,10 +9423,10 @@
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B439" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="C439" t="s">
         <v>217</v>
@@ -9458,13 +9437,13 @@
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B440" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="C440" t="s">
-        <v>217</v>
+        <v>679</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -9472,13 +9451,13 @@
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B441" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="C441" t="s">
-        <v>686</v>
+        <v>158</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -9486,13 +9465,13 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B442" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="C442" t="s">
-        <v>158</v>
+        <v>733</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -9500,13 +9479,13 @@
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B443" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="C443" t="s">
-        <v>740</v>
+        <v>754</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -9514,13 +9493,13 @@
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B444" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C444" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -9528,13 +9507,13 @@
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B445" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="C445" t="s">
-        <v>763</v>
+        <v>707</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -9542,13 +9521,13 @@
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B446" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="C446" t="s">
-        <v>714</v>
+        <v>7</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -9556,13 +9535,13 @@
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B447" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="C447" t="s">
-        <v>7</v>
+        <v>718</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -9570,13 +9549,13 @@
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B448" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C448" t="s">
-        <v>725</v>
+        <v>202</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -9584,13 +9563,13 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B449" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="C449" t="s">
-        <v>202</v>
+        <v>679</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -9598,13 +9577,13 @@
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>667</v>
+        <v>762</v>
       </c>
       <c r="B450" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="C450" t="s">
-        <v>686</v>
+        <v>536</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -9612,13 +9591,13 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B451" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="C451" t="s">
-        <v>536</v>
+        <v>765</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -9626,13 +9605,13 @@
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B452" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="C452" t="s">
-        <v>772</v>
+        <v>25</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -9640,13 +9619,13 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B453" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="C453" t="s">
-        <v>25</v>
+        <v>217</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -9654,13 +9633,13 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
+        <v>762</v>
+      </c>
+      <c r="B454" t="s">
+        <v>768</v>
+      </c>
+      <c r="C454" t="s">
         <v>769</v>
-      </c>
-      <c r="B454" t="s">
-        <v>774</v>
-      </c>
-      <c r="C454" t="s">
-        <v>217</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -9668,13 +9647,13 @@
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B455" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="C455" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -9682,13 +9661,13 @@
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B456" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="C456" t="s">
-        <v>772</v>
+        <v>217</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -9696,13 +9675,13 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B457" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="C457" t="s">
-        <v>217</v>
+        <v>514</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -9710,13 +9689,13 @@
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B458" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="C458" t="s">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -9724,13 +9703,13 @@
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B459" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="C459" t="s">
-        <v>536</v>
+        <v>217</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -9738,13 +9717,13 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B460" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="C460" t="s">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -9752,13 +9731,13 @@
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B461" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="C461" t="s">
-        <v>18</v>
+        <v>217</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -9766,13 +9745,13 @@
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B462" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="C462" t="s">
-        <v>217</v>
+        <v>536</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -9780,13 +9759,13 @@
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B463" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="C463" t="s">
-        <v>536</v>
+        <v>779</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -9794,13 +9773,13 @@
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B464" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="C464" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -9808,13 +9787,13 @@
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B465" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="C465" t="s">
-        <v>788</v>
+        <v>514</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -9822,13 +9801,13 @@
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B466" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="C466" t="s">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -9836,13 +9815,13 @@
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B467" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="C467" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -9850,13 +9829,13 @@
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B468" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="C468" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -9864,13 +9843,13 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B469" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="C469" t="s">
-        <v>29</v>
+        <v>765</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -9878,13 +9857,13 @@
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B470" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="C470" t="s">
-        <v>772</v>
+        <v>536</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -9892,13 +9871,13 @@
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B471" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="C471" t="s">
-        <v>536</v>
+        <v>789</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -9906,13 +9885,13 @@
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B472" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="C472" t="s">
-        <v>796</v>
+        <v>536</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -9920,13 +9899,13 @@
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B473" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="C473" t="s">
-        <v>536</v>
+        <v>792</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -9934,13 +9913,13 @@
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B474" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="C474" t="s">
-        <v>799</v>
+        <v>536</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -9948,10 +9927,10 @@
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B475" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="C475" t="s">
         <v>536</v>
@@ -9962,10 +9941,10 @@
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B476" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="C476" t="s">
         <v>536</v>
@@ -9976,10 +9955,10 @@
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B477" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="C477" t="s">
         <v>536</v>
@@ -9990,10 +9969,10 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B478" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="C478" t="s">
         <v>536</v>
@@ -10004,13 +9983,13 @@
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B479" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="C479" t="s">
-        <v>536</v>
+        <v>679</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -10018,13 +9997,13 @@
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B480" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="C480" t="s">
-        <v>686</v>
+        <v>536</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -10032,13 +10011,13 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B481" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="C481" t="s">
-        <v>536</v>
+        <v>29</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -10046,13 +10025,13 @@
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B482" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="C482" t="s">
-        <v>29</v>
+        <v>536</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -10060,13 +10039,13 @@
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B483" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="C483" t="s">
-        <v>536</v>
+        <v>803</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -10074,13 +10053,13 @@
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B484" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C484" t="s">
-        <v>810</v>
+        <v>536</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -10088,10 +10067,10 @@
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B485" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="C485" t="s">
         <v>536</v>
@@ -10102,10 +10081,10 @@
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B486" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="C486" t="s">
         <v>536</v>
@@ -10116,13 +10095,13 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B487" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="C487" t="s">
-        <v>536</v>
+        <v>18</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -10130,13 +10109,13 @@
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B488" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="C488" t="s">
-        <v>18</v>
+        <v>809</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -10144,13 +10123,13 @@
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B489" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="C489" t="s">
-        <v>816</v>
+        <v>536</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -10158,10 +10137,10 @@
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B490" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="C490" t="s">
         <v>536</v>
@@ -10172,13 +10151,13 @@
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B491" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="C491" t="s">
-        <v>536</v>
+        <v>813</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -10186,13 +10165,13 @@
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B492" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="C492" t="s">
-        <v>820</v>
+        <v>217</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -10200,10 +10179,10 @@
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B493" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="C493" t="s">
         <v>217</v>
@@ -10214,13 +10193,13 @@
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B494" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="C494" t="s">
-        <v>217</v>
+        <v>514</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -10228,13 +10207,13 @@
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B495" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="C495" t="s">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -10242,13 +10221,13 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B496" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="C496" t="s">
-        <v>536</v>
+        <v>819</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -10256,13 +10235,13 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B497" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="C497" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -10270,13 +10249,13 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B498" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="C498" t="s">
-        <v>820</v>
+        <v>765</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -10284,13 +10263,13 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B499" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="C499" t="s">
-        <v>772</v>
+        <v>83</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -10298,13 +10277,13 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B500" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="C500" t="s">
-        <v>83</v>
+        <v>536</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -10312,13 +10291,13 @@
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>769</v>
+        <v>824</v>
       </c>
       <c r="B501" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="C501" t="s">
-        <v>536</v>
+        <v>679</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -10326,13 +10305,13 @@
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B502" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="C502" t="s">
-        <v>686</v>
+        <v>217</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -10340,13 +10319,13 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B503" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="C503" t="s">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -10354,13 +10333,13 @@
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B504" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="C504" t="s">
-        <v>18</v>
+        <v>217</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -10368,13 +10347,13 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B505" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="C505" t="s">
-        <v>217</v>
+        <v>679</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -10382,13 +10361,13 @@
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B506" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="C506" t="s">
-        <v>686</v>
+        <v>217</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -10396,13 +10375,13 @@
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
+        <v>824</v>
+      </c>
+      <c r="B507" t="s">
         <v>831</v>
       </c>
-      <c r="B507" t="s">
-        <v>837</v>
-      </c>
       <c r="C507" t="s">
-        <v>217</v>
+        <v>679</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -10410,13 +10389,13 @@
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B508" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="C508" t="s">
-        <v>686</v>
+        <v>663</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -10424,13 +10403,13 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B509" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="C509" t="s">
-        <v>670</v>
+        <v>18</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -10438,10 +10417,10 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B510" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="C510" t="s">
         <v>18</v>
@@ -10452,10 +10431,10 @@
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B511" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="C511" t="s">
         <v>18</v>
@@ -10466,10 +10445,10 @@
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B512" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="C512" t="s">
         <v>18</v>
@@ -10480,13 +10459,13 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B513" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="C513" t="s">
-        <v>18</v>
+        <v>217</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -10494,13 +10473,13 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B514" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="C514" t="s">
-        <v>217</v>
+        <v>679</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -10508,13 +10487,13 @@
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B515" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="C515" t="s">
-        <v>686</v>
+        <v>18</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -10522,10 +10501,10 @@
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B516" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="C516" t="s">
         <v>18</v>
@@ -10536,10 +10515,10 @@
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B517" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="C517" t="s">
         <v>18</v>
@@ -10550,13 +10529,13 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B518" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="C518" t="s">
-        <v>18</v>
+        <v>679</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -10564,13 +10543,13 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B519" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="C519" t="s">
-        <v>686</v>
+        <v>217</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -10578,13 +10557,13 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B520" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="C520" t="s">
-        <v>217</v>
+        <v>152</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -10592,13 +10571,13 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B521" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="C521" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -10606,13 +10585,13 @@
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B522" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="C522" t="s">
-        <v>18</v>
+        <v>217</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -10620,10 +10599,10 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B523" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="C523" t="s">
         <v>217</v>
@@ -10634,13 +10613,13 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B524" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="C524" t="s">
-        <v>217</v>
+        <v>21</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -10648,13 +10627,13 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B525" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="C525" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -10662,13 +10641,13 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B526" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C526" t="s">
-        <v>101</v>
+        <v>536</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -10676,13 +10655,13 @@
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B527" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="C527" t="s">
-        <v>536</v>
+        <v>852</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -10690,13 +10669,13 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B528" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="C528" t="s">
-        <v>859</v>
+        <v>733</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -10704,13 +10683,13 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B529" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="C529" t="s">
-        <v>740</v>
+        <v>115</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -10718,13 +10697,13 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B530" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="C530" t="s">
-        <v>115</v>
+        <v>217</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -10732,13 +10711,13 @@
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B531" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="C531" t="s">
-        <v>217</v>
+        <v>857</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -10746,13 +10725,13 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B532" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="C532" t="s">
-        <v>864</v>
+        <v>326</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -10760,13 +10739,13 @@
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B533" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="C533" t="s">
-        <v>326</v>
+        <v>536</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -10774,10 +10753,10 @@
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B534" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="C534" t="s">
         <v>536</v>
@@ -10788,10 +10767,10 @@
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B535" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="C535" t="s">
         <v>536</v>
@@ -10802,13 +10781,13 @@
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B536" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="C536" t="s">
-        <v>536</v>
+        <v>681</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -10816,13 +10795,13 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B537" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="C537" t="s">
-        <v>688</v>
+        <v>864</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -10830,13 +10809,13 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B538" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="C538" t="s">
-        <v>871</v>
+        <v>115</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -10844,10 +10823,10 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B539" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="C539" t="s">
         <v>115</v>
@@ -10858,10 +10837,10 @@
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B540" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="C540" t="s">
         <v>115</v>
@@ -10872,10 +10851,10 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B541" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="C541" t="s">
         <v>115</v>
@@ -10886,13 +10865,13 @@
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B542" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="C542" t="s">
-        <v>115</v>
+        <v>265</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -10900,13 +10879,13 @@
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B543" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="C543" t="s">
-        <v>265</v>
+        <v>536</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -10914,13 +10893,13 @@
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B544" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="C544" t="s">
-        <v>536</v>
+        <v>265</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -10928,29 +10907,15 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B545" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="C545" t="s">
-        <v>265</v>
+        <v>115</v>
       </c>
       <c r="D545" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A546" t="s">
-        <v>831</v>
-      </c>
-      <c r="B546" t="s">
-        <v>879</v>
-      </c>
-      <c r="C546" t="s">
-        <v>115</v>
-      </c>
-      <c r="D546" t="s">
         <v>7</v>
       </c>
     </row>
